--- a/DataTables/Datas/battle.xlsx
+++ b/DataTables/Datas/battle.xlsx
@@ -583,12 +583,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2|0|0|0|0|0|0|0|0</t>
+          <t>2|3|2|0|0|0|0|0|0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1|0|0|0|0|0|0|0|0</t>
+          <t>1|3|2|0|0|0|0|0|0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1v1测试战斗</t>
+          <t>3v3多人测试战斗</t>
         </is>
       </c>
     </row>

--- a/DataTables/Datas/battle.xlsx
+++ b/DataTables/Datas/battle.xlsx
@@ -583,12 +583,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2|3|2|0|0|0|0|0|0</t>
+          <t>2|2|2|0|0|0|0|0|0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1|3|2|0|0|0|0|0|0</t>
+          <t>1|2|2|0|0|0|0|0|0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3v3多人测试战斗</t>
+          <t>3v3多人测试战斗(河马+教练)</t>
         </is>
       </c>
     </row>

--- a/DataTables/Datas/battle.xlsx
+++ b/DataTables/Datas/battle.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,11 @@
           <t>comment</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>bg</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -519,6 +524,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -569,6 +579,11 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>战斗背景图(Addressable资源名)</t>
         </is>
       </c>
     </row>
@@ -610,6 +625,11 @@
           <t>3v3多人测试战斗(河马+教练)</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -647,6 +667,11 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>1v2测试战斗</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>default</t>
         </is>
       </c>
     </row>

--- a/DataTables/Datas/battle.xlsx
+++ b/DataTables/Datas/battle.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>battle_bg1</t>
         </is>
       </c>
     </row>
